--- a/site/exports/buaa-hss-public-administration.xlsx
+++ b/site/exports/buaa-hss-public-administration.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>陈文博</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>人文社会科学学院（公共管理学院）</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>博士标签无明确获授句，授位null；本科硕士、学习起止、毕业与授位日期均未知。；诺顿勋爵仅博士阶段师从；正式论文导师未核，导师身份节点不展开、导航关闭。；页面发布日期2026-03-16不是最后更新时间、学位日期或任职日期；全职教师目录不认证实时在岗。；官网两项有作者署名；2016（08）及2016 (08)原样保留，不推卷期月份，外部元数据与全文未核。；必要学术院系职称摘录与无关个人信息分离，未留联系方式或其他非必要信息。；目录归属、来源现任标签与观察日实时在岗状态分开；未知不等于否定。；官网书目未外核出版元数据或全文；阶段师承不等于正式论文导师。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；NEW_RECOVERY：基于留存公开职业来源记录重建；必要事实仍有缺项，不代表完整履历或当前人事认证。；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：公共管理学、Legislatures：China and the World（英文课程）、公共部门决策的理论与实践、西方社会政治思想等；角色未披露；教学／课程开设时间：时间未披露；来源记载的教学内容，不代表当前开课；教学对象层次不属于本人学历。；教学对象层次：未知；原文列表含等，不声称课程完备或授课层次。；来源ID：new-recovery-buaa-chenwenbo-s001-45370506f71d；https://hss.buaa.edu.cn/info/1230/6398.htm；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>buaa</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,13 +692,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="25.2" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="3" max="3"/>
+    <col width="36.4" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1499,8 +1553,122 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>陈文博</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree_label_only</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>政治学博士（Ph.D. in Politics）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>英国赫尔大学（University of Hull）</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>政治学</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>博士学历标签无明确获授动词，授位事实、授位学校和日期仍未知。；label_only_not_explicit_award；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>buaa</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>陈文博</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>来源发布于2026-03-16并有现为措辞，只留必要学术职称与院系；不将发布日期变为任职开始日。；任职按留存来源表述保留；不据此认证当前人事状态。；来源记载（院系）：人文社会科学学院（公共管理学院）</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>buaa</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S13"/>
+  <autoFilter ref="A1:S15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1514,6 +1682,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1525,18 +1695,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="58.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1604,8 +1774,61 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>陈文博</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>诺顿勋爵（The Lord Norton of Louth）</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>doctoral_stage_mentorship</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>师从；来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；博士标签后同句师从支持博士阶段关系，不独立认证正式论文导师；不展开导师实名、身份节点或实时任职。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>buaa</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L2"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1616,15 +1839,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="23.8" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="58.8" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="44.8" customWidth="1" min="6" max="6"/>
     <col width="58.8" customWidth="1" min="7" max="7"/>
     <col width="58.8" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
@@ -1807,8 +2030,112 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>陈文博</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>行政-立法关系研究的兴起与主题</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：陈文博；来源书目信息（期）：（08）；来源书目信息（author_list_status）：author_string_as_official_list；来源书目信息（person_name_as_listed）：陈文博</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>buaa</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>陈文博</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Is the label ‘minimal legislature’ still appropriate? The role of the National People’s Congress in China’s Political System</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_list</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Wenbo Chen；来源书目信息（期）：(08)；来源书目信息（author_list_status）：author_string_as_official_list</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>buaa</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1816,6 +2143,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1827,14 +2158,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="43.4" customWidth="1" min="2" max="2"/>
+    <col width="62.99999999999999" customWidth="1" min="2" max="2"/>
     <col width="58.8" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2061,14 +2392,90 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>陈文博</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-buaa-chenwenbo-s001-45370506f71d</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/info/1230/6398.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T04:21:46.739Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>buaa</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>陈文博</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-buaa-chenwenbo-s002-59c1c6f0cde5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://hss.buaa.edu.cn/szdw1/qzjs1/C.htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T04:21:53.761Z</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>buaa</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>北京航空航天大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
